--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128151514</v>
       </c>
       <c r="B2" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128151514</v>
       </c>
       <c r="B2" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128151514</v>
       </c>
       <c r="B2" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128151535</v>
       </c>
       <c r="B3" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128151556</v>
       </c>
       <c r="B4" t="n">
-        <v>57776</v>
+        <v>57777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128151361</v>
       </c>
       <c r="B5" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>128151618</v>
       </c>
       <c r="B7" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>128151491</v>
       </c>
       <c r="B8" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128151424</v>
       </c>
       <c r="B9" t="n">
-        <v>79108</v>
+        <v>79111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>128151409</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>128151392</v>
       </c>
       <c r="B11" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128151514</v>
       </c>
       <c r="B2" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128151535</v>
       </c>
       <c r="B3" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128151556</v>
       </c>
       <c r="B4" t="n">
-        <v>57777</v>
+        <v>57789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128151361</v>
       </c>
       <c r="B5" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>128151453</v>
       </c>
       <c r="B6" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>128151618</v>
       </c>
       <c r="B7" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>128151491</v>
       </c>
       <c r="B8" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128151424</v>
       </c>
       <c r="B9" t="n">
-        <v>79111</v>
+        <v>79162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>128151409</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>128151392</v>
       </c>
       <c r="B11" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128151361</v>
+        <v>128151453</v>
       </c>
       <c r="B5" t="n">
-        <v>80217</v>
+        <v>56876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,37 +1015,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 35700-2025, Ly lm</t>
+          <t>A 37500-2025, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621317</v>
+        <v>621149</v>
       </c>
       <c r="R5" t="n">
-        <v>7273704</v>
+        <v>7274096</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,18 +1089,12 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på sälg</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128151453</v>
+        <v>128151361</v>
       </c>
       <c r="B6" t="n">
-        <v>56876</v>
+        <v>80217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,46 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 37500-2025, Ly lm</t>
+          <t>A 35700-2025, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621149</v>
+        <v>621317</v>
       </c>
       <c r="R6" t="n">
-        <v>7274096</v>
+        <v>7273704</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,12 +1189,18 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på sälg</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128151453</v>
+        <v>128151361</v>
       </c>
       <c r="B5" t="n">
-        <v>56876</v>
+        <v>80217</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,46 +1015,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 37500-2025, Ly lm</t>
+          <t>A 35700-2025, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621149</v>
+        <v>621317</v>
       </c>
       <c r="R5" t="n">
-        <v>7274096</v>
+        <v>7273704</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,12 +1080,18 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på sälg</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1113,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128151361</v>
+        <v>128151453</v>
       </c>
       <c r="B6" t="n">
-        <v>80217</v>
+        <v>56876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,37 +1121,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 35700-2025, Ly lm</t>
+          <t>A 37500-2025, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621317</v>
+        <v>621149</v>
       </c>
       <c r="R6" t="n">
-        <v>7273704</v>
+        <v>7274096</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,18 +1195,12 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på sälg</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128151514</v>
       </c>
       <c r="B2" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128151535</v>
       </c>
       <c r="B3" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128151556</v>
       </c>
       <c r="B4" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128151361</v>
       </c>
       <c r="B5" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>128151453</v>
       </c>
       <c r="B6" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>128151618</v>
       </c>
       <c r="B7" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>128151491</v>
       </c>
       <c r="B8" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128151424</v>
       </c>
       <c r="B9" t="n">
-        <v>79162</v>
+        <v>79166</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>128151409</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>128151392</v>
       </c>
       <c r="B11" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128151514</v>
       </c>
       <c r="B2" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128151361</v>
+        <v>128151453</v>
       </c>
       <c r="B5" t="n">
-        <v>80221</v>
+        <v>56880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,37 +1015,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 35700-2025, Ly lm</t>
+          <t>A 37500-2025, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621317</v>
+        <v>621149</v>
       </c>
       <c r="R5" t="n">
-        <v>7273704</v>
+        <v>7274096</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,18 +1089,12 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på sälg</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128151453</v>
+        <v>128151361</v>
       </c>
       <c r="B6" t="n">
-        <v>56880</v>
+        <v>80223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,46 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 37500-2025, Ly lm</t>
+          <t>A 35700-2025, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621149</v>
+        <v>621317</v>
       </c>
       <c r="R6" t="n">
-        <v>7274096</v>
+        <v>7273704</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,12 +1189,18 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på sälg</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>128151491</v>
       </c>
       <c r="B8" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128151424</v>
       </c>
       <c r="B9" t="n">
-        <v>79166</v>
+        <v>79168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>128151409</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>128151392</v>
       </c>
       <c r="B11" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128151514</v>
       </c>
       <c r="B2" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128151453</v>
+        <v>128151361</v>
       </c>
       <c r="B5" t="n">
-        <v>56880</v>
+        <v>80223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,46 +1015,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 37500-2025, Ly lm</t>
+          <t>A 35700-2025, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621149</v>
+        <v>621317</v>
       </c>
       <c r="R5" t="n">
-        <v>7274096</v>
+        <v>7273704</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,12 +1080,18 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på sälg</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1113,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128151361</v>
+        <v>128151453</v>
       </c>
       <c r="B6" t="n">
-        <v>80223</v>
+        <v>56880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,37 +1121,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 35700-2025, Ly lm</t>
+          <t>A 37500-2025, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621317</v>
+        <v>621149</v>
       </c>
       <c r="R6" t="n">
-        <v>7273704</v>
+        <v>7274096</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,18 +1195,12 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på sälg</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1750,6 +1750,638 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130562327</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80288</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>621202</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7274019</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130562332</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83161</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>621352</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7273824</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130562330</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80288</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>621212</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7273842</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130562328</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91751</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>621175</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7273748</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130562329</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91727</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>621249</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7273664</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130562331</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83027</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>621350</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7273835</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -1755,7 +1755,7 @@
         <v>130562327</v>
       </c>
       <c r="B12" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>130562332</v>
       </c>
       <c r="B13" t="n">
-        <v>83161</v>
+        <v>83187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>130562330</v>
       </c>
       <c r="B14" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>130562328</v>
       </c>
       <c r="B15" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>130562329</v>
       </c>
       <c r="B16" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>130562331</v>
       </c>
       <c r="B17" t="n">
-        <v>83027</v>
+        <v>83053</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -1861,7 +1861,7 @@
         <v>130562332</v>
       </c>
       <c r="B13" t="n">
-        <v>83187</v>
+        <v>83188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>130562328</v>
       </c>
       <c r="B15" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>130562329</v>
       </c>
       <c r="B16" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>130562331</v>
       </c>
       <c r="B17" t="n">
-        <v>83053</v>
+        <v>83054</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -1861,7 +1861,7 @@
         <v>130562332</v>
       </c>
       <c r="B13" t="n">
-        <v>83188</v>
+        <v>83189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>130562328</v>
       </c>
       <c r="B15" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>130562329</v>
       </c>
       <c r="B16" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>130562331</v>
       </c>
       <c r="B17" t="n">
-        <v>83054</v>
+        <v>83055</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -1755,7 +1755,7 @@
         <v>130562327</v>
       </c>
       <c r="B12" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>130562332</v>
       </c>
       <c r="B13" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>130562330</v>
       </c>
       <c r="B14" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>130562328</v>
       </c>
       <c r="B15" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>130562329</v>
       </c>
       <c r="B16" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>130562331</v>
       </c>
       <c r="B17" t="n">
-        <v>83055</v>
+        <v>83057</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -1755,7 +1755,7 @@
         <v>130562327</v>
       </c>
       <c r="B12" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>130562332</v>
       </c>
       <c r="B13" t="n">
-        <v>83191</v>
+        <v>83199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>130562330</v>
       </c>
       <c r="B14" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>130562328</v>
       </c>
       <c r="B15" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>130562329</v>
       </c>
       <c r="B16" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>130562331</v>
       </c>
       <c r="B17" t="n">
-        <v>83057</v>
+        <v>83065</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -1755,7 +1755,7 @@
         <v>130562327</v>
       </c>
       <c r="B12" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>130562332</v>
       </c>
       <c r="B13" t="n">
-        <v>83199</v>
+        <v>83200</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>130562330</v>
       </c>
       <c r="B14" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>130562328</v>
       </c>
       <c r="B15" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>130562329</v>
       </c>
       <c r="B16" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>130562331</v>
       </c>
       <c r="B17" t="n">
-        <v>83065</v>
+        <v>83066</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 35700-2025 artfynd.xlsx
+++ b/artfynd/A 35700-2025 artfynd.xlsx
@@ -1755,7 +1755,7 @@
         <v>130562327</v>
       </c>
       <c r="B12" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>130562332</v>
       </c>
       <c r="B13" t="n">
-        <v>83200</v>
+        <v>83201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>130562330</v>
       </c>
       <c r="B14" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>130562328</v>
       </c>
       <c r="B15" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>130562329</v>
       </c>
       <c r="B16" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>130562331</v>
       </c>
       <c r="B17" t="n">
-        <v>83066</v>
+        <v>83067</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
